--- a/data/metadata/Informe-01-010046-A-TC-TM-TP.xlsx
+++ b/data/metadata/Informe-01-010046-A-TC-TM-TP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://riamlab-my.sharepoint.com/personal/fernandomartinez_gnoss_com/Documents/Proyectos/AOD/Repositorios/local-data-aragopedia/data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_ACEA37AB45FA40D1AF573C5CD09E481286DC1624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17FFB75A-1AA9-4179-B9D5-46CAD5354C0D}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_ACEA37AB45FA40D1AF573C5CD09E481286DC1624" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E7483DF-E0B5-4FF0-9F24-7F22582D76C5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="915" yWindow="8640" windowWidth="17910" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informe-01-010046-A-TC-TM-TP" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
   <si>
     <t>Código de la provincia</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ganado bovino (cabezas) </t>
+  </si>
+  <si>
+    <t>Ganado bovino (cabezas)</t>
   </si>
 </sst>
 </file>
@@ -227,6 +230,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -566,32 +570,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="46.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,61 +604,64 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -664,58 +672,61 @@
         <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -726,58 +737,61 @@
         <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -794,26 +808,26 @@
         <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="H4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="K4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="M4" s="1" t="s">
         <v>55</v>
       </c>
@@ -821,25 +835,28 @@
         <v>55</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="Q4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>54</v>
       </c>
       <c r="T4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
@@ -856,48 +873,51 @@
         <v>57</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="H5" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="K5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="M5" s="1" t="s">
         <v>57</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="Q5" s="1" t="s">
         <v>57</v>
       </c>
       <c r="R5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>57</v>
       </c>
     </row>
